--- a/Curs Oficial/sesiuni/s05/echipa_verde/Produse.xlsx
+++ b/Curs Oficial/sesiuni/s05/echipa_verde/Produse.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dim_Produse" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produse" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,7 +543,7 @@
         <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>4.68</v>
+        <v>0.03</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         <v>28</v>
       </c>
       <c r="H5" t="n">
-        <v>1.42</v>
+        <v>0.1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         <v>32</v>
       </c>
       <c r="H6" t="n">
-        <v>11.49</v>
+        <v>0.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>89</v>
       </c>
       <c r="H7" t="n">
-        <v>7.38</v>
+        <v>0.05</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5.64</v>
+        <v>0.04</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>79</v>
       </c>
       <c r="H9" t="n">
-        <v>3.04</v>
+        <v>0.08</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>54</v>
       </c>
       <c r="H10" t="n">
-        <v>1.67</v>
+        <v>0.25</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>95</v>
       </c>
       <c r="H11" t="n">
-        <v>3.5</v>
+        <v>0.1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>110</v>
       </c>
       <c r="H12" t="n">
-        <v>8.789999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>18</v>
       </c>
       <c r="H13" t="n">
-        <v>5.25</v>
+        <v>0.03</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -953,7 +953,7 @@
         <v>25</v>
       </c>
       <c r="H14" t="n">
-        <v>6.2</v>
+        <v>0.05</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>42</v>
       </c>
       <c r="H15" t="n">
-        <v>7.16</v>
+        <v>0.42</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>220</v>
       </c>
       <c r="H16" t="n">
-        <v>4.18</v>
+        <v>0.05</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>15</v>
       </c>
       <c r="H17" t="n">
-        <v>6.09</v>
+        <v>0.3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>48</v>
       </c>
       <c r="H18" t="n">
-        <v>2.96</v>
+        <v>0.06</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>59</v>
       </c>
       <c r="H19" t="n">
-        <v>0.44</v>
+        <v>0.02</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>22</v>
       </c>
       <c r="H20" t="n">
-        <v>3.58</v>
+        <v>0.1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>145</v>
       </c>
       <c r="H21" t="n">
-        <v>6.34</v>
+        <v>0.05</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1254,14 +1254,6 @@
           <t>Categorii: fill-down manual daca lipseste</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
